--- a/backend/wp_templates/I/I2 开发支出.xlsx
+++ b/backend/wp_templates/I/I2 开发支出.xlsx
@@ -34,9 +34,6 @@
     <sheet name="可收回金额测试I2-16" sheetId="19" r:id="rId20"/>
     <sheet name="GT_Custom" sheetId="10" state="hidden" r:id="rId21"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId22"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'调整分录汇总I2-3'!$A$1:$J$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'附注披露（上市公司）'!$A$1:$G$58</definedName>
@@ -11077,87 +11074,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="研发费用实质性程序 I6A"/>
-      <sheetName val="附注披露（上市公司）"/>
-      <sheetName val="附注披露（国有企业）"/>
-      <sheetName val="审定表I6-1"/>
-      <sheetName val="明细表I6-2"/>
-      <sheetName val="调整分录汇总I6-3"/>
-      <sheetName val="其他针对性检查表I6-4"/>
-      <sheetName val="截止性测试（账到单据）I6-5"/>
-      <sheetName val="截止性测试（单据到账）I6-6"/>
-      <sheetName val="GT_Custom"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>人工费</v>
-          </cell>
-          <cell r="Q9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>材料费</v>
-          </cell>
-          <cell r="Q10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>制造费用分摊</v>
-          </cell>
-          <cell r="Q11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>无形资产摊销</v>
-          </cell>
-          <cell r="Q12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="Q13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="Q14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="Q15">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -24480,11 +24396,9 @@
     </row>
     <row r="10" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A10" s="279" t="str">
-        <f>'[1]明细表I6-2'!A9</f>
         <v>人工费</v>
       </c>
       <c r="B10" s="240">
-        <f>'[1]明细表I6-2'!Q9</f>
         <v>0</v>
       </c>
       <c r="C10" s="547">
@@ -24518,11 +24432,9 @@
     </row>
     <row r="11" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A11" s="279" t="str">
-        <f>'[1]明细表I6-2'!A10</f>
         <v>材料费</v>
       </c>
       <c r="B11" s="240">
-        <f>'[1]明细表I6-2'!Q10</f>
         <v>0</v>
       </c>
       <c r="C11" s="547">
@@ -24556,11 +24468,9 @@
     </row>
     <row r="12" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A12" s="279" t="str">
-        <f>'[1]明细表I6-2'!A11</f>
         <v>制造费用分摊</v>
       </c>
       <c r="B12" s="240">
-        <f>'[1]明细表I6-2'!Q11</f>
         <v>0</v>
       </c>
       <c r="C12" s="547">
@@ -24594,11 +24504,9 @@
     </row>
     <row r="13" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A13" s="279" t="str">
-        <f>'[1]明细表I6-2'!A12</f>
         <v>无形资产摊销</v>
       </c>
       <c r="B13" s="240">
-        <f>'[1]明细表I6-2'!Q12</f>
         <v>0</v>
       </c>
       <c r="C13" s="547">
@@ -24632,11 +24540,9 @@
     </row>
     <row r="14" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A14" s="283">
-        <f>'[1]明细表I6-2'!A13</f>
         <v>0</v>
       </c>
       <c r="B14" s="240">
-        <f>'[1]明细表I6-2'!Q13</f>
         <v>0</v>
       </c>
       <c r="C14" s="547">
@@ -24670,11 +24576,9 @@
     </row>
     <row r="15" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A15" s="283">
-        <f>'[1]明细表I6-2'!A14</f>
         <v>0</v>
       </c>
       <c r="B15" s="240">
-        <f>'[1]明细表I6-2'!Q14</f>
         <v>0</v>
       </c>
       <c r="C15" s="547">
@@ -24708,11 +24612,9 @@
     </row>
     <row r="16" spans="1:16" s="226" customFormat="1" ht="19.95" customHeight="1">
       <c r="A16" s="283">
-        <f>'[1]明细表I6-2'!A15</f>
         <v>0</v>
       </c>
       <c r="B16" s="240">
-        <f>'[1]明细表I6-2'!Q15</f>
         <v>0</v>
       </c>
       <c r="C16" s="547">
